--- a/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est inquiet. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman. Il dit : maman, je suis inquiet. Il veut raconter. Ewen raconte : le vent fait du bruit. Maman l'écoute. Maman dit : tu es inquiet. Tu as bien raconté. Elle ouvre les bras. Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
+          <t>Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est inquiet. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman. Maman, je suis inquiet. Il veut raconter. Ewen raconte : le vent fait du bruit. Maman l'écoute. Tu es inquiet. Tu as bien raconté. Elle ouvre les bras. Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est inquiet. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman.
+narrateur|Maman, je suis inquiet. Il veut raconter.
+narrateur|Ewen raconte : le vent fait du bruit. Maman l'écoute.
+maman|Tu es inquiet. Tu as bien raconté. Elle ouvre les bras.
+narrateur|Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ewen a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ewen était inquiet. Il a rejoint un adulte. Il a raconté à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ewen s'assoit près de maman. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Ewen a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Ewen était inquiet. Il a rejoint un adulte. Il a raconté à maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Ewen s'assoit près de maman. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ewen est inquiet</t>
+          <t>Aniss raconte le vent</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La gouttière chante. Le vent tape. Aniss a le ventre serré. Il rejoint maman et raconte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est inquiet. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman. Maman, je suis inquiet. Il veut raconter. Ewen raconte : le vent fait du bruit. Maman l'écoute. Tu es inquiet. Tu as bien raconté. Elle ouvre les bras. Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
+          <t>La gouttière chante un petit air. L'eau tombe goutte après goutte. La vitre est toute embuée. La buée fait un petit rond. La maison sent la soupe chaude. Les chaussons d'Aniss sont en laine. Ils sont gris, tout doux. La soupe est presque prête, Aniss. Elle sent bon, maman. Tu as les pieds au chaud ? Oui. Mes chaussons sont doux. Le tapis du salon est épais. Un coussin jaune attend sur le canapé. La lampe fait un rond orange. Tu veux ton camion rouge ? Oui, maman. En ce moment, Aniss est au salon. Il tient le petit camion rouge. Le camion roule tout bas. Il va sous la table. Je te vois, Aniss. Je suis près du canapé. Dehors, le vent souffle fort. La gouttière fait un bruit plus fort. Une branche tape tout doucement. Le ventre d'Aniss se serre. C'est un nœud tout petit. Maman. Mon ventre est serré. Tu peux venir, Aniss. Aniss va vers maman. Maman est l'adulte du canapé. Je suis inquiet. Le vent fait trop de bruit. Tu es inquiet. Tu as bien raconté. Bravo, Aniss. C'est du bon travail. Tu veux un câlin ? Oui, maman. Aniss prend un câlin. Le ventre se desserre un peu. On rejoint un adulte. On raconte. Tu restes près de moi ? Oui. Près de toi. Le vent est dehors. Toi, tu es ici. J'ai raconté le vent. Oui. Tu as raconté. Le camion rouge reste sous la table. La soupe sent encore bon. Tu entends encore la gouttière ? Un peu. Elle chante moins fort. On reste sur le canapé ? Oui. Aniss pose sa main. Dans la main de maman. Le coussin jaune est chaud. Le tapis est doux sous les pieds. Ta main est toute tiède. Le nœud est plus petit. Oui. Parce que tu as raconté. La vitre s'éclaircit un peu. Un rond d'eau glisse tout bas. La soupe va être prête. On reste encore un peu ? Oui. On reste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,87 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est inquiet. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman.
-narrateur|Maman, je suis inquiet. Il veut raconter.
-narrateur|Ewen raconte : le vent fait du bruit. Maman l'écoute.
-maman|Tu es inquiet. Tu as bien raconté. Elle ouvre les bras.
-narrateur|Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La gouttière chante un petit air.
+narrateur|L'eau tombe goutte après goutte.
+narrateur|La vitre est toute embuée.
+narrateur|La buée fait un petit rond.
+narrateur|La maison sent la soupe chaude.
+narrateur|Les chaussons d'Aniss sont en laine.
+narrateur|Ils sont gris, tout doux.
+maman|La soupe est presque prête, Aniss.
+enfant-m|Elle sent bon, maman.
+maman|Tu as les pieds au chaud ?
+enfant-m|Oui.
+enfant-m|Mes chaussons sont doux.
+narrateur|Le tapis du salon est épais.
+narrateur|Un coussin jaune attend sur le canapé.
+narrateur|La lampe fait un rond orange.
+maman|Tu veux ton camion rouge ?
+enfant-m|Oui, maman.
+narrateur|En ce moment, Aniss est au salon.
+narrateur|Il tient le petit camion rouge.
+narrateur|Le camion roule tout bas.
+enfant-m|Il va sous la table.
+maman|Je te vois, Aniss.
+maman|Je suis près du canapé.
+narrateur|Dehors, le vent souffle fort.
+narrateur|La gouttière fait un bruit plus fort.
+narrateur|Une branche tape tout doucement.
+narrateur|Le ventre d'Aniss se serre.
+narrateur|C'est un nœud tout petit.
+enfant-m|Maman.
+enfant-m|Mon ventre est serré.
+maman|Tu peux venir, Aniss.
+narrateur|Aniss va vers maman.
+narrateur|Maman est l'adulte du canapé.
+enfant-m|Je suis inquiet.
+enfant-m|Le vent fait trop de bruit.
+maman|Tu es inquiet.
+maman|Tu as bien raconté.
+maman|Bravo, Aniss.
+maman|C'est du bon travail.
+maman|Tu veux un câlin ?
+enfant-m|Oui, maman.
+narrateur|Aniss prend un câlin.
+narrateur|Le ventre se desserre un peu.
+maman|On rejoint un adulte.
+maman|On raconte.
+maman|Tu restes près de moi ?
+enfant-m|Oui.
+enfant-m|Près de toi.
+maman|Le vent est dehors.
+maman|Toi, tu es ici.
+enfant-m|J'ai raconté le vent.
+maman|Oui.
+maman|Tu as raconté.
+narrateur|Le camion rouge reste sous la table.
+narrateur|La soupe sent encore bon.
+maman|Tu entends encore la gouttière ?
+enfant-m|Un peu.
+enfant-m|Elle chante moins fort.
+maman|On reste sur le canapé ?
+enfant-m|Oui.
+narrateur|Aniss pose sa main.
+narrateur|Dans la main de maman.
+narrateur|Le coussin jaune est chaud.
+narrateur|Le tapis est doux sous les pieds.
+maman|Ta main est toute tiède.
+enfant-m|Le nœud est plus petit.
+maman|Oui.
+maman|Parce que tu as raconté.
+narrateur|La vitre s'éclaircit un peu.
+narrateur|Un rond d'eau glisse tout bas.
+maman|La soupe va être prête.
+enfant-m|On reste encore un peu ?
+maman|Oui.
+maman|On reste.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>gouttiere,vent_dehors</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1429,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ewen a le ventre serré. Que fait-il ?</t>
+          <t>Aniss a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1585,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ewen a le ventre serré. Que fait-il ?</t>
+          <t>narrateur|Aniss a le ventre serré.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1614,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ewen était inquiet. Il a rejoint un adulte. Il a raconté à maman.</t>
+          <t>Aniss était inquiet. Il a rejoint un adulte. Il a raconté à maman. Bravo, Aniss. Tu as raconté. C'est du bon travail. J'étais inquiet. J'ai raconté le vent. Oui. Vers moi, l'adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1758,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ewen était inquiet. Il a rejoint un adulte. Il a raconté à maman.</t>
+          <t>narrateur|Aniss était inquiet.
+narrateur|Il a rejoint un adulte.
+narrateur|Il a raconté à maman.
+maman|Bravo, Aniss.
+maman|Tu as raconté.
+maman|C'est du bon travail.
+enfant-m|J'étais inquiet.
+enfant-m|J'ai raconté le vent.
+maman|Oui.
+maman|Vers moi, l'adulte.
+maman|Tu as le ventre plus doux ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1797,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ewen s'assoit près de maman. Le salon est calme.</t>
+          <t>Aniss s'assoit près de maman. Le salon est calme. On écoute la gouttière ? Oui. Elle chante tout bas. Le vent est loin, maintenant. Le camion rouge dort sous la table. Le coussin jaune est encore chaud. Tu restes contre moi ? Oui. Près de toi. La soupe sent bon, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1933,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ewen s'assoit près de maman. Le salon est calme.</t>
+          <t>narrateur|Aniss s'assoit près de maman.
+narrateur|Le salon est calme.
+maman|On écoute la gouttière ?
+enfant-m|Oui.
+enfant-m|Elle chante tout bas.
+maman|Le vent est loin, maintenant.
+narrateur|Le camion rouge dort sous la table.
+narrateur|Le coussin jaune est encore chaud.
+maman|Tu restes contre moi ?
+enfant-m|Oui.
+enfant-m|Près de toi.
+narrateur|La soupe sent bon, tout près.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1972,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. Tu as fait du bon travail. La gouttière chante encore, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2112,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|J'étais inquiet.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La gouttière chante encore, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière chante un petit air. L'eau tombe goutte après goutte. La vitre est toute embuée. La buée fait un petit rond. La maison sent la soupe chaude. Les chaussons d'Aniss sont en laine. Ils sont gris, tout doux. La soupe est presque prête, Aniss. Elle sent bon, maman. Tu as les pieds au chaud ? Oui. Mes chaussons sont doux. Le tapis du salon est épais. Un coussin jaune attend sur le canapé. La lampe fait un rond orange. Tu veux ton camion rouge ? Oui, maman. En ce moment, Aniss est au salon. Il tient le petit camion rouge. Le camion roule tout bas. Il va sous la table. Je te vois, Aniss. Je suis près du canapé. Dehors, le vent souffle fort. La gouttière fait un bruit plus fort. Une branche tape tout doucement. Le ventre d'Aniss se serre. C'est un nœud tout petit. Maman. Mon ventre est serré. Tu peux venir, Aniss. Aniss va vers maman. Maman est l'adulte du canapé. Je suis inquiet. Le vent fait trop de bruit. Tu es inquiet. Tu as bien raconté. Bravo, Aniss. C'est du bon travail. Tu veux un câlin ? Oui, maman. Aniss prend un câlin. Le ventre se desserre un peu. On rejoint un adulte. On raconte. Tu restes près de moi ? Oui. Près de toi. Le vent est dehors. Toi, tu es ici. J'ai raconté le vent. Oui. Tu as raconté. Le camion rouge reste sous la table. La soupe sent encore bon. Tu entends encore la gouttière ? Un peu. Elle chante moins fort. On reste sur le canapé ? Oui. Aniss pose sa main. Dans la main de maman. Le coussin jaune est chaud. Le tapis est doux sous les pieds. Ta main est toute tiède. Le nœud est plus petit. Oui. Parce que tu as raconté. La vitre s'éclaircit un peu. Un rond d'eau glisse tout bas. La soupe va être prête. On reste encore un peu ? Oui. On reste.</t>
+          <t>La gouttière chante un petit air. L'eau tombe goutte après goutte. La vitre est toute embuée. La buée fait un petit rond. La maison sent la soupe chaude. Les chaussons d'Aniss sont en laine. Ils sont gris, tout doux. La soupe est presque prête, Aniss. Elle sent bon, maman. Tu as les pieds au chaud ? Oui. Mes chaussons sont doux. Le tapis du salon est épais. Un coussin jaune attend sur le canapé. La lampe fait un rond orange. Tu veux ton camion rouge ? Oui, maman. En ce moment, Aniss est au salon. Il tient le petit camion rouge. Le camion roule tout bas. Il va sous la table. Je te vois, Aniss. Je suis près du canapé. Dehors, le vent souffle fort. La gouttière fait un bruit plus fort. Une branche tape tout doucement. Le ventre d'Aniss se serre. C'est un nœud tout petit. Maman. Mon ventre est serré. Tu peux venir, Aniss. Aniss va vers maman. Maman est l'adulte du canapé. Je suis inquiet. Le vent fait trop de bruit. Tu es inquiet. Tu as bien raconté. Bravo, Aniss. Tu veux un câlin ? Oui, maman. Aniss prend un câlin. Le ventre se desserre un peu. On rejoint un adulte. On raconte. Tu restes près de moi ? Oui. Près de toi. Le vent est dehors. Toi, tu es ici. J'ai raconté le vent. Oui. Tu as raconté. Le camion rouge reste sous la table. La soupe sent encore bon. Tu entends encore la gouttière ? Un peu. Elle chante moins fort. On reste sur le canapé ? Oui. Aniss pose sa main. Dans la main de maman. Le coussin jaune est chaud. Le tapis est doux sous les pieds. Ta main est toute tiède. Le nœud est plus petit. Oui. Parce que tu as raconté. La vitre s'éclaircit un peu. Un rond d'eau glisse tout bas. La soupe va être prête. On reste encore un peu ? Oui. On reste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ewen est dans le salon. Dehors, le vent souffle fort. Le ventre d'Ewen est serré. Ewen est &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Inquiet, c'est le ventre serré. Maman est près du canapé. Maman est un adulte. Ewen va vers maman. Il dit : maman, je suis inquiet. Il veut raconter. Ewen raconte : le vent fait du bruit. Maman l'écoute. Maman dit : tu es inquiet. Tu as bien raconté. Elle ouvre les bras. Ewen prend un câlin. Le ventre se desserre un peu. Ewen reste près de l'adulte. Il a raconté. Maman est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière chante un petit air. L'eau tombe goutte après goutte. La vitre est toute embuée. La buée fait un petit rond. La maison sent la soupe chaude. Les chaussons d'Aniss sont en laine. Ils sont gris, tout doux. La soupe est presque prête, Aniss. Elle sent bon, maman. Tu as les pieds au chaud ? Oui. Mes chaussons sont doux. Le tapis du salon est épais. Un coussin jaune attend sur le canapé. La lampe fait un rond orange. Tu veux ton camion rouge ? Oui, maman. En ce moment, Aniss est au salon. Il tient le petit camion rouge. Le camion roule tout bas. Il va sous la table. Je te vois, Aniss. Je suis près du canapé. Dehors, le vent souffle fort. La gouttière fait un bruit plus fort. Une branche tape tout doucement. Le ventre d'Aniss se serre. C'est un nœud tout petit. Maman. Mon ventre est serré. Tu peux venir, Aniss. Aniss va vers maman. Maman est l'adulte du canapé. Je suis inquiet. Le vent fait trop de bruit. Tu es inquiet. Tu as bien raconté. Bravo, Aniss. Tu veux un câlin ? Oui, maman. Aniss prend un câlin. Le ventre se desserre un peu. On rejoint un adulte. On raconte. Tu restes près de moi ? Oui. Près de toi. Le vent est dehors. Toi, tu es ici. J'ai raconté le vent. Oui. Tu as raconté. Le camion rouge reste sous la table. La soupe sent encore bon. Tu entends encore la gouttière ? Un peu. Elle chante moins fort. On reste sur le canapé ? Oui. Aniss pose sa main. Dans la main de maman. Le coussin jaune est chaud. Le tapis est doux sous les pieds. Ta main est toute tiède. Le nœud est plus petit. Oui. Parce que tu as raconté. La vitre s'éclaircit un peu. Un rond d'eau glisse tout bas. La soupe va être prête. On reste encore un peu ? Oui. On reste.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 maman|Tu es inquiet.
 maman|Tu as bien raconté.
 maman|Bravo, Aniss.
-maman|C'est du bon travail.
 maman|Tu veux un câlin ?
 enfant-m|Oui, maman.
 narrateur|Aniss prend un câlin.
@@ -1434,7 +1433,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ewen a le ventre serré. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a le ventre serré. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1589,7 +1588,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,12 +1612,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss était inquiet. Il a rejoint un adulte. Il a raconté à maman. Bravo, Aniss. Tu as raconté. C'est du bon travail. J'étais inquiet. J'ai raconté le vent. Oui. Vers moi, l'adulte. Tu as le ventre plus doux ? Oui, maman.</t>
+          <t>Aniss était inquiet. Il a rejoint un adulte. Il a raconté à maman. Bravo, Aniss. Tu as raconté. J'étais inquiet. J'ai raconté le vent. Oui. Vers moi, l'adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ewen était &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Il a rejoint un adulte. Il a raconté à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss était inquiet. Il a rejoint un adulte. Il a raconté à maman. Bravo, Aniss. Tu as raconté. J'étais inquiet. J'ai raconté le vent. Oui. Vers moi, l'adulte. Tu as le ventre plus doux ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,7 +1761,6 @@
 narrateur|Il a raconté à maman.
 maman|Bravo, Aniss.
 maman|Tu as raconté.
-maman|C'est du bon travail.
 enfant-m|J'étais inquiet.
 enfant-m|J'ai raconté le vent.
 maman|Oui.
@@ -1772,7 +1769,6 @@
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1802,7 +1798,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ewen s'assoit près de maman. Le salon est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss s'assoit près de maman. Le salon est calme. On écoute la gouttière ? Oui. Elle chante tout bas. Le vent est loin, maintenant. Le camion rouge dort sous la table. Le coussin jaune est encore chaud. Tu restes contre moi ? Oui. Près de toi. La soupe sent bon, tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1947,7 +1943,6 @@
 narrateur|La soupe sent bon, tout près.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1972,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. J'étais inquiet. Bravo. Tu as fait du bon travail. La gouttière chante encore, tout doux. L'histoire est finie.</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. La gouttière chante encore, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. J'étais inquiet. Bravo. La gouttière chante encore, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2115,12 +2110,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|J'étais inquiet.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La gouttière chante encore, tout doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La gouttière chante encore, tout doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2176,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ewen, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
